--- a/dist/checklists/xlsx/tol/spatial_transcriptomics_image_manifest_version_tol_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/tol/spatial_transcriptomics_image_manifest_version_tol_stx_fish_v0.1.xlsx
@@ -880,7 +880,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="8E01" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="845B" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -947,7 +947,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="B6C7" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A0EC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4130,7 +4130,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DDC7" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DB46" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8220,7 +8220,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AE19" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D3EF" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12442,7 +12442,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EE23" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EDDC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17538,7 +17538,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A1B8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C37C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/tol/spatial_transcriptomics_image_manifest_version_tol_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/tol/spatial_transcriptomics_image_manifest_version_tol_stx_fish_v0.1.xlsx
@@ -880,7 +880,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="845B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BC78" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -947,7 +947,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="A0EC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8E3B" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4130,7 +4130,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DB46" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9668" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8220,7 +8220,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D3EF" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="87F0" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12442,7 +12442,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EDDC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DDD6" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17538,7 +17538,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C37C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E083" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/tol/spatial_transcriptomics_image_manifest_version_tol_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/tol/spatial_transcriptomics_image_manifest_version_tol_stx_fish_v0.1.xlsx
@@ -880,7 +880,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="BC78" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B897" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -947,7 +947,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="8E3B" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BB65" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4130,7 +4130,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9668" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DD1C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8220,7 +8220,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="87F0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D674" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12442,7 +12442,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DDD6" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F48D" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17538,7 +17538,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="E083" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BDAA" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
